--- a/牛只数据集/134个数据集信息收集/cowcv_ruchay2026_screening.xlsx
+++ b/牛只数据集/134个数据集信息收集/cowcv_ruchay2026_screening.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LYX10\Downloads\Typora\牛只数据集\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LYX10\Downloads\Typora\牛只数据集\134个数据集信息收集\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -4528,7 +4528,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4536,7 +4536,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4990,10 +4990,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -5120,8 +5120,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -5796,10 +5799,10 @@
       <c r="S2" t="s">
         <v>39</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="V2" s="1">
+      <c r="V2" s="2">
         <v>46055</v>
       </c>
     </row>
@@ -5864,7 +5867,7 @@
       <c r="T3" t="s">
         <v>53</v>
       </c>
-      <c r="V3" s="1">
+      <c r="V3" s="2">
         <v>46084</v>
       </c>
     </row>
@@ -5929,7 +5932,7 @@
       <c r="T4" t="s">
         <v>69</v>
       </c>
-      <c r="V4" s="1">
+      <c r="V4" s="2">
         <v>46116</v>
       </c>
     </row>
@@ -5994,7 +5997,7 @@
       <c r="T5" t="s">
         <v>80</v>
       </c>
-      <c r="V5" s="1">
+      <c r="V5" s="2">
         <v>46147</v>
       </c>
     </row>
@@ -6059,7 +6062,7 @@
       <c r="T6" t="s">
         <v>94</v>
       </c>
-      <c r="V6" s="1">
+      <c r="V6" s="2">
         <v>46179</v>
       </c>
     </row>
@@ -6124,7 +6127,7 @@
       <c r="T7" t="s">
         <v>105</v>
       </c>
-      <c r="V7" s="1">
+      <c r="V7" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -6189,7 +6192,7 @@
       <c r="T8" t="s">
         <v>116</v>
       </c>
-      <c r="V8" s="1">
+      <c r="V8" s="2">
         <v>46242</v>
       </c>
     </row>
@@ -6254,7 +6257,7 @@
       <c r="T9" t="s">
         <v>127</v>
       </c>
-      <c r="V9" s="1">
+      <c r="V9" s="2">
         <v>46274</v>
       </c>
     </row>
@@ -6316,7 +6319,7 @@
       <c r="T10" t="s">
         <v>140</v>
       </c>
-      <c r="V10" s="1">
+      <c r="V10" s="2">
         <v>46305</v>
       </c>
     </row>
@@ -6381,7 +6384,7 @@
       <c r="T11" t="s">
         <v>150</v>
       </c>
-      <c r="V11" s="1">
+      <c r="V11" s="2">
         <v>46337</v>
       </c>
     </row>
@@ -6446,7 +6449,7 @@
       <c r="T12" t="s">
         <v>162</v>
       </c>
-      <c r="V12" s="1">
+      <c r="V12" s="2">
         <v>46368</v>
       </c>
     </row>
@@ -8747,7 +8750,7 @@
       <c r="T48" t="s">
         <v>580</v>
       </c>
-      <c r="V48" s="1">
+      <c r="V48" s="2">
         <v>46055</v>
       </c>
     </row>
@@ -8812,7 +8815,7 @@
       <c r="T49" t="s">
         <v>580</v>
       </c>
-      <c r="V49" s="1">
+      <c r="V49" s="2">
         <v>46084</v>
       </c>
     </row>
@@ -8877,7 +8880,7 @@
       <c r="T50" t="s">
         <v>555</v>
       </c>
-      <c r="V50" s="1">
+      <c r="V50" s="2">
         <v>46116</v>
       </c>
     </row>
@@ -8939,7 +8942,7 @@
       <c r="T51" t="s">
         <v>612</v>
       </c>
-      <c r="V51" s="1">
+      <c r="V51" s="2">
         <v>46148</v>
       </c>
     </row>
@@ -9004,7 +9007,7 @@
       <c r="T52" t="s">
         <v>623</v>
       </c>
-      <c r="V52" s="1">
+      <c r="V52" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -9069,7 +9072,7 @@
       <c r="T53" t="s">
         <v>635</v>
       </c>
-      <c r="V53" s="1">
+      <c r="V53" s="2">
         <v>46242</v>
       </c>
     </row>
@@ -9134,7 +9137,7 @@
       <c r="T54" t="s">
         <v>647</v>
       </c>
-      <c r="V54" s="1">
+      <c r="V54" s="2">
         <v>46274</v>
       </c>
     </row>
@@ -9199,7 +9202,7 @@
       <c r="T55" t="s">
         <v>658</v>
       </c>
-      <c r="V55" s="1">
+      <c r="V55" s="2">
         <v>46305</v>
       </c>
     </row>
@@ -9264,7 +9267,7 @@
       <c r="T56" t="s">
         <v>669</v>
       </c>
-      <c r="V56" s="1">
+      <c r="V56" s="2">
         <v>46337</v>
       </c>
     </row>
@@ -9329,7 +9332,7 @@
       <c r="T57" t="s">
         <v>680</v>
       </c>
-      <c r="V57" s="1">
+      <c r="V57" s="2">
         <v>46369</v>
       </c>
     </row>
@@ -14416,6 +14419,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="T2" r:id="rId1" display="https://github.com/Oliver6999/cattle_dataset" tooltip="https://github.com/Oliver6999/cattle_dataset"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
